--- a/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,50 +475,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>coach_away</t>
+          <t>season</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>country</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -527,85 +507,60 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AszX60rp</t>
+          <t>hQiNHHd2</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mendoza r 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.8125</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">allianz field
+  saint paul  mn </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71000</v>
+        <v>19400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>l6eEjGlO</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>valentino rob</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>zoZ995af</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nancy wilfried</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="O2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="P2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -614,18 +569,13 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jix3jCxF</t>
+          <t>C6QBlj7R</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villarreal a 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -647,52 +597,32 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>K4FYmLD9</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>courtois laurent</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>xA45kovo</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>herdman john</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="O3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -701,259 +631,184 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h6Py6Kcj</t>
+          <t>dbI3Q902</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">de oliveira m 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>74867</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>167</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>zkH7PTF8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>167</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>UPVAOmVE</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">chase stadium
   fort lauderdale  fl </t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>21550</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0AheRyBg</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>inter miami</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6gpXy3vi</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>martino gerardo</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>6LuGZiZI</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>klopas frank</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>167</v>
       </c>
-      <c r="O4" t="n">
+      <c r="K6" t="n">
         <v>1671</v>
       </c>
-      <c r="P4" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="M6" t="n">
         <v>2024</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>WdOu5vDd</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>68756</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>new england revolution</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>GzULyFoh</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>porter caleb</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>WWvwigh8</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>luccin peter</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>167</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>KCHNTNkc</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unkel t 
-  usa </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>zV5YmQAr</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>new york red bulls</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>fc cincinnati</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>rJ9D8rzj</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>schwarz sandro</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>roEEsq76</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>noonan pat</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>167</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -962,85 +817,60 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>b3GRSs53</t>
+          <t>8GUEN7pL</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25500</v>
+        <v>54251</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>K4zRMgTN</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>pareja oscar</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>dp6AQn9c</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>cushing nicholas</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>167</v>
       </c>
-      <c r="O7" t="n">
+      <c r="K7" t="n">
         <v>1671</v>
       </c>
-      <c r="P7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="M7" t="n">
         <v>2024</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1049,18 +879,13 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>tS5WR1K9</t>
+          <t>juKJMRaR</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45493.85416666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">penso c 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">subaru park
@@ -1082,52 +907,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>6BusaLE3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>curtin jim</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>63fk89be</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>callaghan brian</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>167</v>
       </c>
-      <c r="O8" t="n">
+      <c r="K8" t="n">
         <v>1671</v>
       </c>
-      <c r="P8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="M8" t="n">
         <v>2024</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1136,69 +941,60 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h29zRLZF</t>
+          <t>Usy7kWiL</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45493.89583333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freemon j 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>20738</v>
+        <v>54405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>charlotte</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>167</v>
       </c>
-      <c r="O9" t="n">
+      <c r="K9" t="n">
         <v>1671</v>
       </c>
-      <c r="P9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="M9" t="n">
         <v>2024</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1207,69 +1003,60 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>QF7rPa4S</t>
+          <t>lSHwpAFr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45493.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pekmic i 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.89583333334</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19400</v>
+        <v>22039</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v>167</v>
       </c>
-      <c r="O10" t="n">
+      <c r="K10" t="n">
         <v>1671</v>
       </c>
-      <c r="P10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="M10" t="n">
         <v>2024</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1278,140 +1065,122 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>nP8vQukM</t>
+          <t>MNAkH5Nl</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45493.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vazquez r 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.89583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>167</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>S0BoIo8r</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45528.89583333334</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">children s mercy park
   kansas city  ks </t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>21650</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>CURGfJWt</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>sporting kansas city</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>167</v>
       </c>
-      <c r="O11" t="n">
+      <c r="K12" t="n">
         <v>1671</v>
       </c>
-      <c r="P11" t="n">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="M12" t="n">
         <v>2024</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>69kBKJCq</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45493.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">touchan r 
-  usa </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>18061</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>167</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1420,213 +1189,310 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>vNmJIcsd</t>
+          <t>0E9gGPxe</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45493.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chapman a 
-  usa </t>
-        </is>
-      </c>
+        <v>45528.9375</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>20213</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>167</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Ik4bFqh1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.97916666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>167</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dt32E377</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">providence park
+  portland  or </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25218</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>167</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vqenBDBt</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45531.875</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>dtMNCXyk</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>indy eleven</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>167</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SWX9C8ZI</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45531.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
   seattle  wa </t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E17" t="n">
         <v>72000</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>seattle sounders</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>los angeles fc</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
+      <c r="J17" t="n">
         <v>167</v>
       </c>
-      <c r="O13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="K17" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>2024</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>MHXbihN8</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45493.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bazakos f 
-  usa </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>54405</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>167</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>p0lFJwSk</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45493.98958333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>167</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>mls</t>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>us open cup</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,30 +507,30 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.8125</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19400</v>
+        <v>20371</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,40 +569,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23112</v>
+        <v>68756</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -631,40 +631,40 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>74867</v>
+        <v>25000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -693,40 +693,40 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20000</v>
+        <v>61500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>O6hjfSXE</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>dc united</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -755,40 +755,40 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21550</v>
+        <v>22039</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -817,40 +817,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.97916666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54251</v>
+        <v>54405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -873,626 +873,6 @@
       <c r="O7" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>columbus crew</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>167</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>54405</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>167</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22039</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>167</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>167</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>167</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45528.9375</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>167</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>167</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>167</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vqenBDBt</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45531.875</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>dtMNCXyk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>indy eleven</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>167</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1672</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>us open cup</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SWX9C8ZI</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45531.97916666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>167</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1672</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>us open cup</t>
         </is>
       </c>
     </row>

--- a/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">lower com field
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -699,7 +714,12 @@
       <c r="B5" s="2" t="n">
         <v>45542.89583333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">soldier field
@@ -761,7 +781,12 @@
       <c r="B6" s="2" t="n">
         <v>45542.89583333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -823,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45542.97916666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place
@@ -871,6 +901,812 @@
         </is>
       </c>
       <c r="O7" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>167</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>167</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>167</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>167</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>167</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>167</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>167</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>167</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>167</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>167</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.9375</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>167</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>167</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>167</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>mls</t>
         </is>

--- a/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,12 @@
       <c r="B2" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">mercedes benz stadium
@@ -575,7 +580,12 @@
       <c r="B3" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -637,7 +647,12 @@
       <c r="B4" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">audi field
@@ -699,7 +714,12 @@
       <c r="B5" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">tql stadium
@@ -761,7 +781,12 @@
       <c r="B6" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">chase stadium
@@ -823,7 +848,12 @@
       <c r="B7" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso t 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">inter co stadium
@@ -885,7 +915,12 @@
       <c r="B8" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo field
@@ -947,7 +982,12 @@
       <c r="B9" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">soldier field
@@ -1009,7 +1049,12 @@
       <c r="B10" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -1071,7 +1116,12 @@
       <c r="B11" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">citypark
@@ -1133,7 +1183,12 @@
       <c r="B12" s="2" t="n">
         <v>45549.9375</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">dick s sporting goods park
@@ -1195,7 +1250,12 @@
       <c r="B13" s="2" t="n">
         <v>45549.97916666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">dignity health sports park
@@ -1257,7 +1317,12 @@
       <c r="B14" s="2" t="n">
         <v>45549.97916666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place
@@ -1319,7 +1384,12 @@
       <c r="B15" s="2" t="n">
         <v>45550.84375</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
@@ -1367,812 +1437,6 @@
         </is>
       </c>
       <c r="O15" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>71000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0AheRyBg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>inter miami</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>167</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>68756</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>new england revolution</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>167</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>54251</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>167</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>30991</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>columbus crew</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>167</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45553.88541666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>QJF7WTFB</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>charlotte</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>167</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>22039</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>167</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>19400</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>fc cincinnati</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>167</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>167</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>167</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45553.9375</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>167</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>167</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>167</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>167</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
         <is>
           <t>mls</t>
         </is>

--- a/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,45 +507,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71000</v>
+        <v>54251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -574,45 +574,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23112</v>
+        <v>74867</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -641,45 +641,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20000</v>
+        <v>23112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,45 +708,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26000</v>
+        <v>20371</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -775,45 +775,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">penso c 
+  usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21550</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -842,45 +842,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso t 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25500</v>
+        <v>20738</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -909,45 +909,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30991</v>
+        <v>20500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -976,45 +976,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>61500</v>
+        <v>30000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1043,45 +1043,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>21650</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1110,45 +1110,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22423</v>
+        <v>18061</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1177,35 +1177,35 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45549.9375</v>
+        <v>45556.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">penso t 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18061</v>
+        <v>20213</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1244,15 +1244,15 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1311,45 +1311,45 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
+          <t xml:space="preserve">montero r 
+  cos </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54405</v>
+        <v>18000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1370,73 +1370,6 @@
         </is>
       </c>
       <c r="O14" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45550.84375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>167</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
         <is>
           <t>mls</t>
         </is>

--- a/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/data/usa/p6_deployment/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,30 +475,50 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -507,65 +527,85 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45556.625</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54251</v>
+        <v>71000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>inter miami</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>valentino rob</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>schwarz sandro</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>167</v>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>1671</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>2024</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -574,15 +614,15 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>UuWb8pb0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.70833333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
@@ -607,32 +647,52 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>new england revolution</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>smith dean</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>courtois laurent</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
         <v>167</v>
       </c>
-      <c r="K3" t="n">
+      <c r="O3" t="n">
         <v>1671</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>2024</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -641,65 +701,85 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>llHizuVJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23112</v>
+        <v>20371</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>Szrwix67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nancy wilfried</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>curtin jim</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
         <v>167</v>
       </c>
-      <c r="K4" t="n">
+      <c r="O4" t="n">
         <v>1671</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>2024</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -708,35 +788,35 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20371</v>
+        <v>26000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -749,24 +829,44 @@
           <t>orlando city</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>noonan pat</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>pareja oscar</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>167</v>
       </c>
-      <c r="K5" t="n">
+      <c r="O5" t="n">
         <v>1671</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>2024</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -775,65 +875,85 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25000</v>
+        <v>68756</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>O6hjfSXE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>porter caleb</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lesesne troy</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>167</v>
       </c>
-      <c r="K6" t="n">
+      <c r="O6" t="n">
         <v>1671</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>2024</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -842,65 +962,85 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>MFWf9Qrf</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20738</v>
+        <v>54405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>sartini vanni</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ramsay eric</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>167</v>
       </c>
-      <c r="K7" t="n">
+      <c r="O7" t="n">
         <v>1671</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>2024</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -909,35 +1049,35 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20500</v>
+        <v>21650</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -950,24 +1090,28 @@
           <t>los angeles fc</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
         <v>167</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
         <v>1671</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>2024</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -976,65 +1120,69 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">penso t 
+  usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30000</v>
+        <v>22423</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
         <v>167</v>
       </c>
-      <c r="K9" t="n">
+      <c r="O9" t="n">
         <v>1671</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>2024</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1043,65 +1191,69 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.9375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pekmic i 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21650</v>
+        <v>18061</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
         <v>167</v>
       </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
         <v>1671</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>2024</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1110,65 +1262,69 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18061</v>
+        <v>27000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
         <v>167</v>
       </c>
-      <c r="K11" t="n">
+      <c r="O11" t="n">
         <v>1671</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>2024</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1177,65 +1333,69 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso t 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20213</v>
+        <v>18000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>real salt lake</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
         <v>167</v>
       </c>
-      <c r="K12" t="n">
+      <c r="O12" t="n">
         <v>1671</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>2024</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1244,65 +1404,69 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.70833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27000</v>
+        <v>54251</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="n">
         <v>167</v>
       </c>
-      <c r="K13" t="n">
+      <c r="O13" t="n">
         <v>1671</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>2024</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
@@ -1311,65 +1475,69 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.83333333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">montero r 
-  cos </t>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18000</v>
+        <v>25218</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
         <v>167</v>
       </c>
-      <c r="K14" t="n">
+      <c r="O14" t="n">
         <v>1671</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
         <v>2024</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
